--- a/config/demo/forms/app/cbac_referral_review_high_risk.xlsx
+++ b/config/demo/forms/app/cbac_referral_review_high_risk.xlsx
@@ -824,7 +824,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>source_cbac_id</t>
+          <t>cbac_source_id</t>
         </is>
       </c>
     </row>
